--- a/reports/2026-03-10.xlsx
+++ b/reports/2026-03-10.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-10 05:15 UTC</t>
+          <t>2026-03-10 08:23 UTC</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -642,7 +642,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-10_1773119650949</t>
+          <t>2026-03-10_1773130910028</t>
         </is>
       </c>
     </row>
@@ -950,10 +950,10 @@
         <v>0.01277457242734036</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01629</v>
+        <v>0.01615</v>
       </c>
       <c r="Q2" t="n">
-        <v>27.51894509702624</v>
+        <v>26.42301800595297</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -979,22 +979,22 @@
         <v>0.8678855515323745</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06140620202640217</v>
+        <v>0.06186204763377417</v>
       </c>
       <c r="Z2" t="n">
-        <v>25610.1686087</v>
+        <v>28319.5096706</v>
       </c>
       <c r="AA2" t="n">
-        <v>23696.1654921</v>
+        <v>22025.0322487</v>
       </c>
       <c r="AB2" t="n">
-        <v>29.82605</v>
+        <v>25.053244</v>
       </c>
       <c r="AC2" t="n">
-        <v>41.232567</v>
+        <v>37.685416</v>
       </c>
       <c r="AD2" t="n">
-        <v>46327157.39808404</v>
+        <v>45655964.29468115</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HSKUSDT</t>
+          <t>JSTUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HashKey Platform Token</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>85.42</v>
+        <v>84.25</v>
       </c>
       <c r="I3" t="n">
-        <v>85.42</v>
+        <v>84.25</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -1061,13 +1061,13 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1647712192355553</v>
+        <v>0.04695144039995708</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1751</v>
+        <v>0.04969</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.268558800720392</v>
+        <v>5.83274885011924</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -1075,40 +1075,40 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.1430857449882901</v>
+        <v>0.04260101184770685</v>
       </c>
       <c r="T3" t="n">
-        <v>13.16095999524277</v>
+        <v>9.265804233461186</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1812483411591109</v>
+        <v>0.05164658443995279</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1977254630826664</v>
+        <v>0.05634172847994849</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7598229919105191</v>
+        <v>1.079237133446815</v>
       </c>
       <c r="X3" t="n">
-        <v>1.519645983821037</v>
+        <v>2.158474266893627</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3998857469294523</v>
+        <v>0.04029008863819336</v>
       </c>
       <c r="Z3" t="n">
-        <v>12207.136468</v>
+        <v>7631.8484652</v>
       </c>
       <c r="AA3" t="n">
-        <v>13372.669085</v>
+        <v>8392.6092716</v>
       </c>
       <c r="AB3" t="n">
-        <v>69.675461</v>
+        <v>20.422324</v>
       </c>
       <c r="AC3" t="n">
-        <v>105.935658</v>
+        <v>1334.364649</v>
       </c>
       <c r="AD3" t="n">
-        <v>60384046.25277323</v>
+        <v>438891896.1926882</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FLOWUSDT</t>
+          <t>PLUMEUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Flow</t>
+          <t>Plume</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1138,33 +1138,29 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>72.81</v>
+        <v>76</v>
       </c>
       <c r="I4" t="n">
-        <v>72.81</v>
+        <v>76</v>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>none</t>
@@ -1179,13 +1175,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04095743408211393</v>
+        <v>0.01253255917263749</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06023</v>
+        <v>0.013442</v>
       </c>
       <c r="Q4" t="n">
-        <v>47.05511062838374</v>
+        <v>7.256625042298648</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1193,40 +1189,40 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.02884907216233867</v>
+        <v>0.01085812351615938</v>
       </c>
       <c r="T4" t="n">
-        <v>29.56328244464654</v>
+        <v>13.36068422588366</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04505317749032533</v>
+        <v>0.01378581508990124</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04914892089853672</v>
+        <v>0.01503907100716499</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3382574319588402</v>
+        <v>0.7484646617593886</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6765148639176803</v>
+        <v>1.496929323518775</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.116482236458941</v>
+        <v>0.1114206128133659</v>
       </c>
       <c r="Z4" t="n">
-        <v>3468.6414927</v>
+        <v>22159.30407799</v>
       </c>
       <c r="AA4" t="n">
-        <v>4061.175674</v>
+        <v>5702.09655045</v>
       </c>
       <c r="AB4" t="n">
-        <v>51.739877</v>
+        <v>62.099106</v>
       </c>
       <c r="AC4" t="n">
-        <v>3191.10057</v>
+        <v>148.166065</v>
       </c>
       <c r="AD4" t="n">
-        <v>98929647.89094122</v>
+        <v>68550049.38241813</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -1241,12 +1237,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HUMAUSDT</t>
+          <t>FLOWUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Huma Finance</t>
+          <t>Flow</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1256,7 +1252,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1270,10 +1266,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>70.58</v>
+        <v>72.81</v>
       </c>
       <c r="I5" t="n">
-        <v>70.58</v>
+        <v>72.81</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1297,54 +1293,54 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01480590889108883</v>
+        <v>0.04095743408211393</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01494</v>
+        <v>0.06263000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9056594221775516</v>
+        <v>52.91485270887723</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.009558651609544486</v>
+        <v>0.02884907216233867</v>
       </c>
       <c r="T5" t="n">
-        <v>35.44029157644276</v>
+        <v>29.56328244464654</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01628649978019771</v>
+        <v>0.04505317749032533</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0177670906693066</v>
+        <v>0.04914892089853672</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2821647214281676</v>
+        <v>0.3382574319588402</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5643294428563346</v>
+        <v>0.6765148639176803</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06682258603408839</v>
+        <v>0.09598464245720294</v>
       </c>
       <c r="Z5" t="n">
-        <v>14335.644516</v>
+        <v>3279.2183065</v>
       </c>
       <c r="AA5" t="n">
-        <v>5669.90755</v>
+        <v>5999.4443411</v>
       </c>
       <c r="AB5" t="n">
-        <v>29.041092</v>
+        <v>32.827614</v>
       </c>
       <c r="AC5" t="n">
-        <v>188.914299</v>
+        <v>328.146194</v>
       </c>
       <c r="AD5" t="n">
-        <v>43228045.89360473</v>
+        <v>102899763.6300063</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1359,12 +1355,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZROUSDT</t>
+          <t>HUMAUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LayerZero</t>
+          <t>Huma Finance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1374,7 +1370,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1388,15 +1384,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.23</v>
+        <v>70.58</v>
       </c>
       <c r="I6" t="n">
-        <v>70.23</v>
+        <v>70.58</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>none</t>
@@ -1411,13 +1411,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.809059641689167</v>
+        <v>0.01480590889108883</v>
       </c>
       <c r="P6" t="n">
-        <v>2.061</v>
+        <v>0.01584</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.92659216451202</v>
+        <v>6.984313604236436</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1425,40 +1425,40 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>1.45153993680352</v>
+        <v>0.009558651609544486</v>
       </c>
       <c r="T6" t="n">
-        <v>19.76273731648897</v>
+        <v>35.44029157644276</v>
       </c>
       <c r="U6" t="n">
-        <v>1.989965605858084</v>
+        <v>0.01628649978019771</v>
       </c>
       <c r="V6" t="n">
-        <v>2.170871570027</v>
+        <v>0.0177670906693066</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5060027788588042</v>
+        <v>0.2821647214281676</v>
       </c>
       <c r="X6" t="n">
-        <v>1.012005557717607</v>
+        <v>0.5643294428563346</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.097087378640766</v>
+        <v>0.1896933291179183</v>
       </c>
       <c r="Z6" t="n">
-        <v>269948.76136</v>
+        <v>4103.940233</v>
       </c>
       <c r="AA6" t="n">
-        <v>131838.40112</v>
+        <v>4373.9176381</v>
       </c>
       <c r="AB6" t="n">
-        <v>14.69053</v>
+        <v>55.954433</v>
       </c>
       <c r="AC6" t="n">
-        <v>36.955392</v>
+        <v>299.025182</v>
       </c>
       <c r="AD6" t="n">
-        <v>629717887.1709698</v>
+        <v>46463674.47931626</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PLUMEUSDT</t>
+          <t>JELLYJELLYUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plume</t>
+          <t>Jelly-My-Jelly</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_too_early</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1502,15 +1502,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>70</v>
+        <v>69.89</v>
       </c>
       <c r="I7" t="n">
-        <v>70</v>
+        <v>69.89</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>none</t>
@@ -1525,54 +1529,54 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01075295701235112</v>
+        <v>0.07254456795701304</v>
       </c>
       <c r="P7" t="n">
-        <v>0.013512</v>
+        <v>0.05553</v>
       </c>
       <c r="Q7" t="n">
-        <v>25.65845826854676</v>
+        <v>-23.45395173777198</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>early</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0.008212466013312127</v>
+        <v>0.04886657722349436</v>
       </c>
       <c r="T7" t="n">
-        <v>23.62597559090878</v>
+        <v>32.63923323321644</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01182825271358623</v>
+        <v>0.07979902475271436</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01290354841482134</v>
+        <v>0.08705348154841565</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4232629446992226</v>
+        <v>0.3063797463790655</v>
       </c>
       <c r="X7" t="n">
-        <v>0.8465258893984445</v>
+        <v>0.6127594927581297</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1555843674754469</v>
+        <v>0.08588913144615723</v>
       </c>
       <c r="Z7" t="n">
-        <v>15743.67035886</v>
+        <v>2513.76236903</v>
       </c>
       <c r="AA7" t="n">
-        <v>3429.90485316</v>
+        <v>3438.00253641</v>
       </c>
       <c r="AB7" t="n">
-        <v>84.015901</v>
+        <v>94.291988</v>
       </c>
       <c r="AC7" t="n">
-        <v>164.606211</v>
+        <v>1248.971317</v>
       </c>
       <c r="AD7" t="n">
-        <v>69072383.40338774</v>
+        <v>55697354.6766426</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1587,12 +1591,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEXEUSDT</t>
+          <t>ETHFIUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DeXe</t>
+          <t>ether.fi</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1607,19 +1611,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>68</v>
+        <v>69.72</v>
       </c>
       <c r="I8" t="n">
-        <v>68</v>
+        <v>69.72</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -1639,13 +1643,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.183278238439226</v>
+        <v>0.5128955151615413</v>
       </c>
       <c r="P8" t="n">
-        <v>5.358</v>
+        <v>0.5909</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.0813681185849</v>
+        <v>15.20865020897881</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1653,40 +1657,40 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>3.74720222979964</v>
+        <v>0.4351343353948764</v>
       </c>
       <c r="T8" t="n">
-        <v>10.42426498511572</v>
+        <v>15.1612126579374</v>
       </c>
       <c r="U8" t="n">
-        <v>4.60160606228315</v>
+        <v>0.5641850666776955</v>
       </c>
       <c r="V8" t="n">
-        <v>5.019933886127071</v>
+        <v>0.6154746181938495</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9593002493968175</v>
+        <v>0.6595778468132416</v>
       </c>
       <c r="X8" t="n">
-        <v>1.918600498793631</v>
+        <v>1.319155693626481</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.09327488107454121</v>
+        <v>0.1014198782961349</v>
       </c>
       <c r="Z8" t="n">
-        <v>4738.05605</v>
+        <v>167156.726897</v>
       </c>
       <c r="AA8" t="n">
-        <v>2771.53642</v>
+        <v>134848.106851</v>
       </c>
       <c r="AB8" t="n">
-        <v>75.748559</v>
+        <v>14.00342</v>
       </c>
       <c r="AC8" t="n">
-        <v>8698.646107</v>
+        <v>22.51467</v>
       </c>
       <c r="AD8" t="n">
-        <v>446390123.728236</v>
+        <v>438078036.8556407</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1701,12 +1705,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KERNELUSDT</t>
+          <t>HSKUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KernelDAO</t>
+          <t>HashKey Platform Token</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1721,19 +1725,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>68</v>
+        <v>68.33</v>
       </c>
       <c r="I9" t="n">
-        <v>68</v>
+        <v>68.33</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -1753,13 +1757,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0860465988689619</v>
+        <v>0.1647712192355553</v>
       </c>
       <c r="P9" t="n">
-        <v>0.09858</v>
+        <v>0.1742</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.56582978965255</v>
+        <v>5.722346905114173</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1767,47 +1771,51 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0.07748115540034986</v>
+        <v>0.1430857449882901</v>
       </c>
       <c r="T9" t="n">
-        <v>9.954424208743138</v>
+        <v>13.16095999524277</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0946512587558581</v>
+        <v>0.1812483411591109</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1032559186427543</v>
+        <v>0.1977254630826664</v>
       </c>
       <c r="W9" t="n">
-        <v>1.004578445754486</v>
+        <v>0.7598229919105191</v>
       </c>
       <c r="X9" t="n">
-        <v>2.009156891508969</v>
+        <v>1.519645983821037</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1014610389610419</v>
+        <v>0.1148105625717599</v>
       </c>
       <c r="Z9" t="n">
-        <v>3470.1780872</v>
+        <v>7354.298086999999</v>
       </c>
       <c r="AA9" t="n">
-        <v>4664.564229699999</v>
+        <v>7456.095217</v>
       </c>
       <c r="AB9" t="n">
-        <v>59.357213</v>
+        <v>83.2081</v>
       </c>
       <c r="AC9" t="n">
-        <v>259.021276</v>
+        <v>140.581816</v>
       </c>
       <c r="AD9" t="n">
-        <v>28361027.5860717</v>
+        <v>60315172.13616227</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>low_liquidity</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1815,12 +1823,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RESOLVUSDT</t>
+          <t>DEXEUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Resolv</t>
+          <t>DeXe</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1867,13 +1875,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1016028864626002</v>
+        <v>4.271727929672502</v>
       </c>
       <c r="P10" t="n">
-        <v>0.13277</v>
+        <v>5.007</v>
       </c>
       <c r="Q10" t="n">
-        <v>30.67542136105785</v>
+        <v>17.21252107888503</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1881,40 +1889,40 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>0.08232148938568476</v>
+        <v>3.813657346888133</v>
       </c>
       <c r="T10" t="n">
-        <v>18.9772138845808</v>
+        <v>10.72330893553624</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1117631751088602</v>
+        <v>4.698900722639753</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1219234637551202</v>
+        <v>5.126073515607002</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5269477416874727</v>
+        <v>0.9325479719101223</v>
       </c>
       <c r="X10" t="n">
-        <v>1.053895483374945</v>
+        <v>1.865095943820243</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1053027453930058</v>
+        <v>0.06009013520280648</v>
       </c>
       <c r="Z10" t="n">
-        <v>23849.6126583</v>
+        <v>5355.859799999999</v>
       </c>
       <c r="AA10" t="n">
-        <v>19932.7422026</v>
+        <v>1727.21575</v>
       </c>
       <c r="AB10" t="n">
-        <v>14.017169</v>
+        <v>166.788482</v>
       </c>
       <c r="AC10" t="n">
-        <v>41.591686</v>
+        <v>10141.64879</v>
       </c>
       <c r="AD10" t="n">
-        <v>49001781.62156559</v>
+        <v>423550402.3537126</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1929,12 +1937,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ETHFIUSDT</t>
+          <t>KERNELUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ether.fi</t>
+          <t>KernelDAO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1949,19 +1957,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>66.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="I11" t="n">
-        <v>66.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -1981,13 +1989,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5128955151615413</v>
+        <v>0.08729454180475003</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5698</v>
+        <v>0.09702</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.0947518853886</v>
+        <v>11.14096940562757</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1995,40 +2003,40 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>0.4351343353948764</v>
+        <v>0.07876377145832388</v>
       </c>
       <c r="T11" t="n">
-        <v>15.1612126579374</v>
+        <v>9.77239833105117</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5641850666776955</v>
+        <v>0.09602399598522504</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6154746181938495</v>
+        <v>0.1047534501657</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6595778468132416</v>
+        <v>1.023290257031956</v>
       </c>
       <c r="X11" t="n">
-        <v>1.319155693626481</v>
+        <v>2.046580514063909</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.07028641714989756</v>
+        <v>0.09275003864584208</v>
       </c>
       <c r="Z11" t="n">
-        <v>188311.068934</v>
+        <v>7200.732469</v>
       </c>
       <c r="AA11" t="n">
-        <v>116048.946933</v>
+        <v>4860.5145074</v>
       </c>
       <c r="AB11" t="n">
-        <v>18.77578</v>
+        <v>59.907251</v>
       </c>
       <c r="AC11" t="n">
-        <v>25.364507</v>
+        <v>349.74818</v>
       </c>
       <c r="AD11" t="n">
-        <v>423741099.4982876</v>
+        <v>27836537.21127053</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -2043,12 +2051,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HYPEUSDT</t>
+          <t>RESOLVUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>Resolv</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2072,10 +2080,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>66.28</v>
+        <v>68</v>
       </c>
       <c r="I12" t="n">
-        <v>66.28</v>
+        <v>68</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -2095,13 +2103,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>31.83467695631397</v>
+        <v>0.1043340400839963</v>
       </c>
       <c r="P12" t="n">
-        <v>34.41</v>
+        <v>0.13192</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.089678582949311</v>
+        <v>26.44003806791628</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2109,40 +2117,40 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>29.61432412197418</v>
+        <v>0.08515131429352707</v>
       </c>
       <c r="T12" t="n">
-        <v>6.974635983857247</v>
+        <v>18.3858746148676</v>
       </c>
       <c r="U12" t="n">
-        <v>35.01814465194536</v>
+        <v>0.114767444092396</v>
       </c>
       <c r="V12" t="n">
-        <v>38.20161234757676</v>
+        <v>0.1252008481007956</v>
       </c>
       <c r="W12" t="n">
-        <v>1.433766582678284</v>
+        <v>0.5438958009598079</v>
       </c>
       <c r="X12" t="n">
-        <v>2.867533165356567</v>
+        <v>1.087791601919614</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.02904022070567158</v>
+        <v>0.06080875646092789</v>
       </c>
       <c r="Z12" t="n">
-        <v>40282.4288</v>
+        <v>19562.4372455</v>
       </c>
       <c r="AA12" t="n">
-        <v>48928.3347</v>
+        <v>19712.8213739</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.549594000000001</v>
+        <v>10.95754</v>
       </c>
       <c r="AC12" t="n">
-        <v>23.179276</v>
+        <v>38.441606</v>
       </c>
       <c r="AD12" t="n">
-        <v>8917380623.247444</v>
+        <v>49060574.63594389</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2157,12 +2165,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ASTERUSDT</t>
+          <t>BANANAS31USDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Banana For Scale</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2172,7 +2180,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | rebound_not_confirmed | entry_late</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2186,81 +2194,77 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>66.01000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="I13" t="n">
-        <v>66.01000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>rebound_not_confirmed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N13" t="b">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6982908334499303</v>
+        <v>0.006809922886232783</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7055</v>
+        <v>0.007104</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.032401716409859</v>
+        <v>4.318361876927201</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0.6735077527570139</v>
+        <v>0.005682970381366535</v>
       </c>
       <c r="T13" t="n">
-        <v>3.549105831802871</v>
+        <v>16.54868232274027</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7681199167949233</v>
+        <v>0.007490915174856062</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8379490001399162</v>
+        <v>0.008171907463479339</v>
       </c>
       <c r="W13" t="n">
-        <v>2.817611103729813</v>
+        <v>0.6042777186107787</v>
       </c>
       <c r="X13" t="n">
-        <v>5.635222207459622</v>
+        <v>1.208555437221556</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.08500991782373675</v>
+        <v>0.03236314260184683</v>
       </c>
       <c r="Z13" t="n">
-        <v>272340.287483</v>
+        <v>11261.921104275</v>
       </c>
       <c r="AA13" t="n">
-        <v>301898.949243</v>
+        <v>16788.513957556</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.418803</v>
+        <v>12.625253</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.884558</v>
+        <v>67.31598</v>
       </c>
       <c r="AD13" t="n">
-        <v>1748458099.412923</v>
+        <v>70954642.91152386</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2275,12 +2279,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GRASSUSDT</t>
+          <t>ASTERUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2290,7 +2294,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>risk_reward_unattractive | entry_not_confirmed | rebound_not_confirmed | entry_late</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2304,77 +2308,81 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>63.7</v>
+        <v>64.41</v>
       </c>
       <c r="I14" t="n">
-        <v>63.7</v>
+        <v>64.41</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>rebound_not_confirmed</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N14" t="b">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3095512849297625</v>
+        <v>0.6988536108816352</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3407</v>
+        <v>0.7054</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.06253780445627</v>
+        <v>0.9367325311671948</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>0.2759275774058372</v>
+        <v>0.674769322150654</v>
       </c>
       <c r="T14" t="n">
-        <v>10.86207977833287</v>
+        <v>3.44625660595755</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3405064134227388</v>
+        <v>0.7687389719697988</v>
       </c>
       <c r="V14" t="n">
-        <v>0.371461541915715</v>
+        <v>0.8386243330579622</v>
       </c>
       <c r="W14" t="n">
-        <v>0.9206340041754714</v>
+        <v>2.901699189408295</v>
       </c>
       <c r="X14" t="n">
-        <v>1.841268008350941</v>
+        <v>5.803398378816586</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1761597181444479</v>
+        <v>0.08504606661940949</v>
       </c>
       <c r="Z14" t="n">
-        <v>12958.329419</v>
+        <v>304227.556439</v>
       </c>
       <c r="AA14" t="n">
-        <v>10480.741347</v>
+        <v>289935.137229</v>
       </c>
       <c r="AB14" t="n">
-        <v>25.801726</v>
+        <v>4.481129</v>
       </c>
       <c r="AC14" t="n">
-        <v>88.493881</v>
+        <v>8.212991000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>83727347.12359154</v>
+        <v>1747329530.404762</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2389,12 +2397,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JSTUSDT</t>
+          <t>ZROUSDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>LayerZero</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2404,7 +2412,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2418,10 +2426,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>60.72</v>
+        <v>63.84</v>
       </c>
       <c r="I15" t="n">
-        <v>60.72</v>
+        <v>63.84</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
@@ -2429,25 +2437,25 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N15" t="b">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.04695144039995708</v>
+        <v>1.809059641689167</v>
       </c>
       <c r="P15" t="n">
-        <v>0.04892</v>
+        <v>2.09</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.19275656566378</v>
+        <v>15.52963494606023</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -2455,51 +2463,47 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>0.04260101184770685</v>
+        <v>1.45153993680352</v>
       </c>
       <c r="T15" t="n">
-        <v>9.265804233461186</v>
+        <v>19.76273731648897</v>
       </c>
       <c r="U15" t="n">
-        <v>0.05164658443995279</v>
+        <v>1.989965605858084</v>
       </c>
       <c r="V15" t="n">
-        <v>0.05634172847994849</v>
+        <v>2.170871570027</v>
       </c>
       <c r="W15" t="n">
-        <v>1.079237133446815</v>
+        <v>0.5060027788588042</v>
       </c>
       <c r="X15" t="n">
-        <v>2.158474266893627</v>
+        <v>1.012005557717607</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.04093327875562666</v>
+        <v>0.04774409166867195</v>
       </c>
       <c r="Z15" t="n">
-        <v>6247.6581127</v>
+        <v>250255.13371</v>
       </c>
       <c r="AA15" t="n">
-        <v>5977.2138833</v>
+        <v>258891.88298</v>
       </c>
       <c r="AB15" t="n">
-        <v>18.481371</v>
+        <v>11.317355</v>
       </c>
       <c r="AC15" t="n">
-        <v>1588.661755</v>
+        <v>18.04571</v>
       </c>
       <c r="AD15" t="n">
-        <v>430728418.6121929</v>
+        <v>634507928.4806006</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>low_liquidity</t>
-        </is>
-      </c>
+      <c r="AF15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2507,12 +2511,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARIAUSDT</t>
+          <t>GRASSUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AriaAI</t>
+          <t>Grass</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2536,10 +2540,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>60</v>
+        <v>63.7</v>
       </c>
       <c r="I16" t="n">
-        <v>60</v>
+        <v>63.7</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
@@ -2559,13 +2563,13 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08790349969395152</v>
+        <v>0.3133178291831258</v>
       </c>
       <c r="P16" t="n">
-        <v>0.09830999999999999</v>
+        <v>0.3503</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.83855061775718</v>
+        <v>11.80340452163005</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -2573,40 +2577,40 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0.07630897740900021</v>
+        <v>0.2799958140645221</v>
       </c>
       <c r="T16" t="n">
-        <v>13.19005764880725</v>
+        <v>10.63521192058558</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09669384966334668</v>
+        <v>0.3446496121014385</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1054841996327418</v>
+        <v>0.375981395019751</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7581468001320142</v>
+        <v>0.9402727538173404</v>
       </c>
       <c r="X16" t="n">
-        <v>1.516293600264026</v>
+        <v>1.880545507634678</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1626181522512525</v>
+        <v>0.2284408909194811</v>
       </c>
       <c r="Z16" t="n">
-        <v>2026.055775</v>
+        <v>15112.444803</v>
       </c>
       <c r="AA16" t="n">
-        <v>1610.5165121</v>
+        <v>11268.231585</v>
       </c>
       <c r="AB16" t="n">
-        <v>1466.69687</v>
+        <v>28.289455</v>
       </c>
       <c r="AC16" t="n">
-        <v>8047.898426</v>
+        <v>88.34151</v>
       </c>
       <c r="AD16" t="n">
-        <v>29076157.00210513</v>
+        <v>85506449.44058512</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2650,10 +2654,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>61.6</v>
       </c>
       <c r="I17" t="n">
-        <v>60</v>
+        <v>61.6</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
@@ -2673,13 +2677,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>6.055137123420731e-07</v>
+        <v>6.141600255281821e-07</v>
       </c>
       <c r="P17" t="n">
-        <v>7.016e-07</v>
+        <v>6.975e-07</v>
       </c>
       <c r="Q17" t="n">
-        <v>15.8685568467597</v>
+        <v>13.56974908944046</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2687,40 +2691,40 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>5.329280817721169e-07</v>
+        <v>5.413733749520684e-07</v>
       </c>
       <c r="T17" t="n">
-        <v>11.98744621144936</v>
+        <v>11.85141454192117</v>
       </c>
       <c r="U17" t="n">
-        <v>6.660650835762805e-07</v>
+        <v>6.755760280810004e-07</v>
       </c>
       <c r="V17" t="n">
-        <v>7.266164548104877e-07</v>
+        <v>7.369920306338185e-07</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8342060371832062</v>
+        <v>0.843781133857711</v>
       </c>
       <c r="X17" t="n">
-        <v>1.668412074366411</v>
+        <v>1.687562267715421</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.3277520484502973</v>
+        <v>0.2009184845005739</v>
       </c>
       <c r="Z17" t="n">
-        <v>18378.0391123466</v>
+        <v>7116.111486257299</v>
       </c>
       <c r="AA17" t="n">
-        <v>1769.2288294618</v>
+        <v>1396.2923070611</v>
       </c>
       <c r="AB17" t="n">
-        <v>107.694043</v>
+        <v>121.934412</v>
       </c>
       <c r="AC17" t="n">
-        <v>367.457897</v>
+        <v>467.635157</v>
       </c>
       <c r="AD17" t="n">
-        <v>95363477.17809518</v>
+        <v>94820394.1330146</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2750,7 +2754,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_too_early</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2787,54 +2791,54 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0503303642758196</v>
+        <v>0.05046366290388034</v>
       </c>
       <c r="P18" t="n">
-        <v>0.04987</v>
+        <v>0.05411</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9146849669053103</v>
+        <v>7.22566870158623</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>early</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>0.04216385097867353</v>
+        <v>0.04109761567127466</v>
       </c>
       <c r="T18" t="n">
-        <v>16.22581798214708</v>
+        <v>18.55998295336877</v>
       </c>
       <c r="U18" t="n">
-        <v>0.05536340070340157</v>
+        <v>0.05551002919426837</v>
       </c>
       <c r="V18" t="n">
-        <v>0.06039643713098351</v>
+        <v>0.0605563954846564</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6163017489166218</v>
+        <v>0.5387935983090399</v>
       </c>
       <c r="X18" t="n">
-        <v>1.232603497833241</v>
+        <v>1.077587196618079</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1399580125962224</v>
+        <v>0.1661896408457203</v>
       </c>
       <c r="Z18" t="n">
-        <v>7298.2201687</v>
+        <v>3781.1641676</v>
       </c>
       <c r="AA18" t="n">
-        <v>6929.7036642</v>
+        <v>3557.2393987</v>
       </c>
       <c r="AB18" t="n">
-        <v>28.517431</v>
+        <v>64.661563</v>
       </c>
       <c r="AC18" t="n">
-        <v>615.0045239999999</v>
+        <v>2749.865532</v>
       </c>
       <c r="AD18" t="n">
-        <v>81991464.84679775</v>
+        <v>87634425.46512368</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2904,10 +2908,10 @@
         <v>0.02037303259900328</v>
       </c>
       <c r="P19" t="n">
-        <v>0.02189</v>
+        <v>0.022</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.445957756288757</v>
+        <v>7.985887192249996</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2933,22 +2937,22 @@
         <v>1.32217430473046</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.04571428571428385</v>
+        <v>0.09099181073702996</v>
       </c>
       <c r="Z19" t="n">
-        <v>360.0180703</v>
+        <v>533.9647105</v>
       </c>
       <c r="AA19" t="n">
-        <v>910.6369639</v>
+        <v>700.7587344999999</v>
       </c>
       <c r="AB19" t="n">
-        <v>3335.754284</v>
+        <v>2276.155788</v>
       </c>
       <c r="AC19" t="n">
-        <v>11915.064514</v>
+        <v>10542.607935</v>
       </c>
       <c r="AD19" t="n">
-        <v>54032374.71883883</v>
+        <v>54222242.09075253</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2967,12 +2971,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OKBUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OKB</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2987,19 +2991,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>59.44</v>
+        <v>59.88</v>
       </c>
       <c r="I20" t="n">
-        <v>59.44</v>
+        <v>59.88</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
@@ -3019,13 +3023,13 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>85.88863072603141</v>
+        <v>32.09613629253965</v>
       </c>
       <c r="P20" t="n">
-        <v>98.95699999999999</v>
+        <v>35</v>
       </c>
       <c r="Q20" t="n">
-        <v>15.21548214647201</v>
+        <v>9.047393371567015</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -3033,40 +3037,40 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>70.62689155836354</v>
+        <v>29.88866586910107</v>
       </c>
       <c r="T20" t="n">
-        <v>17.76921932350971</v>
+        <v>6.877682732023061</v>
       </c>
       <c r="U20" t="n">
-        <v>94.47749379863455</v>
+        <v>35.30574992179362</v>
       </c>
       <c r="V20" t="n">
-        <v>103.0663568712377</v>
+        <v>38.51536355104759</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5627709252690368</v>
+        <v>1.453978089660806</v>
       </c>
       <c r="X20" t="n">
-        <v>1.125541850538073</v>
+        <v>2.907956179321611</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.06066182046121998</v>
+        <v>0.02855103497501216</v>
       </c>
       <c r="Z20" t="n">
-        <v>35248.223398</v>
+        <v>49924.3747</v>
       </c>
       <c r="AA20" t="n">
-        <v>35599.836116</v>
+        <v>68965.6753</v>
       </c>
       <c r="AB20" t="n">
-        <v>18.432866</v>
+        <v>7.897409</v>
       </c>
       <c r="AC20" t="n">
-        <v>27.900923</v>
+        <v>11.855813</v>
       </c>
       <c r="AD20" t="n">
-        <v>2079950560.456228</v>
+        <v>9003873488.356989</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3081,12 +3085,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KAVAUSDT</t>
+          <t>OKBUSDT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kava</t>
+          <t>OKB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3110,10 +3114,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>58.5</v>
+        <v>59.44</v>
       </c>
       <c r="I21" t="n">
-        <v>58.5</v>
+        <v>59.44</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
@@ -3133,13 +3137,13 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.05793259189678349</v>
+        <v>85.88863072603141</v>
       </c>
       <c r="P21" t="n">
-        <v>0.06805</v>
+        <v>98.51900000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>17.4641040077101</v>
+        <v>14.70551942346956</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -3147,40 +3151,40 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>0.04580796253663064</v>
+        <v>70.62689155836354</v>
       </c>
       <c r="T21" t="n">
-        <v>20.92885707885277</v>
+        <v>17.76921932350971</v>
       </c>
       <c r="U21" t="n">
-        <v>0.06372585108646185</v>
+        <v>94.47749379863455</v>
       </c>
       <c r="V21" t="n">
-        <v>0.06951911027614019</v>
+        <v>103.0663568712377</v>
       </c>
       <c r="W21" t="n">
-        <v>0.4778091781277611</v>
+        <v>0.5627709252690368</v>
       </c>
       <c r="X21" t="n">
-        <v>0.9556183562555205</v>
+        <v>1.125541850538073</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1176297603293585</v>
+        <v>0.06191039231905881</v>
       </c>
       <c r="Z21" t="n">
-        <v>4695.8636115</v>
+        <v>33978.826989</v>
       </c>
       <c r="AA21" t="n">
-        <v>6328.2578164</v>
+        <v>32922.089988</v>
       </c>
       <c r="AB21" t="n">
-        <v>39.779955</v>
+        <v>9.20429</v>
       </c>
       <c r="AC21" t="n">
-        <v>4283.646316</v>
+        <v>16.628542</v>
       </c>
       <c r="AD21" t="n">
-        <v>73781836.44678672</v>
+        <v>2070312245.137269</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>

--- a/reports/2026-03-10.xlsx
+++ b/reports/2026-03-10.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-10 08:23 UTC</t>
+          <t>2026-03-10 18:09 UTC</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -642,7 +642,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-10_1773130910028</t>
+          <t>2026-03-10_1773166018029</t>
         </is>
       </c>
     </row>
@@ -950,10 +950,10 @@
         <v>0.01277457242734036</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01615</v>
+        <v>0.01499</v>
       </c>
       <c r="Q2" t="n">
-        <v>26.42301800595297</v>
+        <v>17.34247925134582</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -979,22 +979,22 @@
         <v>0.8678855515323745</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06186204763377417</v>
+        <v>0.06677796327211748</v>
       </c>
       <c r="Z2" t="n">
-        <v>28319.5096706</v>
+        <v>27863.2159811</v>
       </c>
       <c r="AA2" t="n">
-        <v>22025.0322487</v>
+        <v>21262.0574909</v>
       </c>
       <c r="AB2" t="n">
-        <v>25.053244</v>
+        <v>17.956026</v>
       </c>
       <c r="AC2" t="n">
-        <v>37.685416</v>
+        <v>36.991484</v>
       </c>
       <c r="AD2" t="n">
-        <v>45655964.29468115</v>
+        <v>42625868.55331103</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JSTUSDT</t>
+          <t>MNTUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>Mantle</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1038,15 +1038,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>84.25</v>
+        <v>74.89</v>
       </c>
       <c r="I3" t="n">
-        <v>84.25</v>
+        <v>74.89</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>none</t>
@@ -1061,13 +1065,13 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04695144039995708</v>
+        <v>0.6609831913680313</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04969</v>
+        <v>0.6983</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.83274885011924</v>
+        <v>5.645651677576624</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -1075,40 +1079,40 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.04260101184770685</v>
+        <v>0.5918392684538851</v>
       </c>
       <c r="T3" t="n">
-        <v>9.265804233461186</v>
+        <v>10.46076871804252</v>
       </c>
       <c r="U3" t="n">
-        <v>0.05164658443995279</v>
+        <v>0.7270815105048345</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05634172847994849</v>
+        <v>0.7931798296416376</v>
       </c>
       <c r="W3" t="n">
-        <v>1.079237133446815</v>
+        <v>0.955952690432034</v>
       </c>
       <c r="X3" t="n">
-        <v>2.158474266893627</v>
+        <v>1.911905380864066</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04029008863819336</v>
+        <v>0.1146460303812013</v>
       </c>
       <c r="Z3" t="n">
-        <v>7631.8484652</v>
+        <v>27553.130155</v>
       </c>
       <c r="AA3" t="n">
-        <v>8392.6092716</v>
+        <v>25684.162706</v>
       </c>
       <c r="AB3" t="n">
-        <v>20.422324</v>
+        <v>16.590029</v>
       </c>
       <c r="AC3" t="n">
-        <v>1334.364649</v>
+        <v>26.590544</v>
       </c>
       <c r="AD3" t="n">
-        <v>438891896.1926882</v>
+        <v>2286884011.892895</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -1123,12 +1127,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PLUMEUSDT</t>
+          <t>ZROUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plume</t>
+          <t>LayerZero</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1138,24 +1142,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
+          <t>risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>76</v>
+        <v>74.88</v>
       </c>
       <c r="I4" t="n">
-        <v>76</v>
+        <v>74.88</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -1163,25 +1167,25 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01253255917263749</v>
+        <v>1.809059641689167</v>
       </c>
       <c r="P4" t="n">
-        <v>0.013442</v>
+        <v>2.101</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.256625042298648</v>
+        <v>16.13768565630265</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1189,40 +1193,40 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.01085812351615938</v>
+        <v>1.45153993680352</v>
       </c>
       <c r="T4" t="n">
-        <v>13.36068422588366</v>
+        <v>19.76273731648897</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01378581508990124</v>
+        <v>1.989965605858084</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01503907100716499</v>
+        <v>2.170871570027</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7484646617593886</v>
+        <v>0.5060027788588042</v>
       </c>
       <c r="X4" t="n">
-        <v>1.496929323518775</v>
+        <v>1.012005557717607</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1114206128133659</v>
+        <v>0.04763038818765849</v>
       </c>
       <c r="Z4" t="n">
-        <v>22159.30407799</v>
+        <v>235848.32927</v>
       </c>
       <c r="AA4" t="n">
-        <v>5702.09655045</v>
+        <v>244981.63146</v>
       </c>
       <c r="AB4" t="n">
-        <v>62.099106</v>
+        <v>7.931026</v>
       </c>
       <c r="AC4" t="n">
-        <v>148.166065</v>
+        <v>20.892768</v>
       </c>
       <c r="AD4" t="n">
-        <v>68550049.38241813</v>
+        <v>640211298.3074648</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -1296,10 +1300,10 @@
         <v>0.04095743408211393</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06263000000000001</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>52.91485270887723</v>
+        <v>67.49096113410469</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1325,22 +1329,22 @@
         <v>0.6765148639176803</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09598464245720294</v>
+        <v>0.07265857734504759</v>
       </c>
       <c r="Z5" t="n">
-        <v>3279.2183065</v>
+        <v>5973.986422</v>
       </c>
       <c r="AA5" t="n">
-        <v>5999.4443411</v>
+        <v>4330.3459894</v>
       </c>
       <c r="AB5" t="n">
-        <v>32.827614</v>
+        <v>53.991435</v>
       </c>
       <c r="AC5" t="n">
-        <v>328.146194</v>
+        <v>366.144092</v>
       </c>
       <c r="AD5" t="n">
-        <v>102899763.6300063</v>
+        <v>113914847.0584328</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1355,12 +1359,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HUMAUSDT</t>
+          <t>PLUMEUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Huma Finance</t>
+          <t>Plume</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1370,33 +1374,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.58</v>
+        <v>72.8</v>
       </c>
       <c r="I6" t="n">
-        <v>70.58</v>
+        <v>72.8</v>
       </c>
       <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>none</t>
@@ -1411,13 +1411,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01480590889108883</v>
+        <v>0.01273526045097429</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01584</v>
+        <v>0.013313</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.984313604236436</v>
+        <v>4.536535010412823</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1425,40 +1425,40 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.009558651609544486</v>
+        <v>0.01110056842311257</v>
       </c>
       <c r="T6" t="n">
-        <v>35.44029157644276</v>
+        <v>12.83595285824457</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01628649978019771</v>
+        <v>0.01400878649607172</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0177670906693066</v>
+        <v>0.01528231254116915</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2821647214281676</v>
+        <v>0.7790617580507063</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5643294428563346</v>
+        <v>1.558123516101412</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1896933291179183</v>
+        <v>0.09020521686837449</v>
       </c>
       <c r="Z6" t="n">
-        <v>4103.940233</v>
+        <v>15488.50322502</v>
       </c>
       <c r="AA6" t="n">
-        <v>4373.9176381</v>
+        <v>12853.33300608</v>
       </c>
       <c r="AB6" t="n">
-        <v>55.954433</v>
+        <v>29.960646</v>
       </c>
       <c r="AC6" t="n">
-        <v>299.025182</v>
+        <v>78.482252</v>
       </c>
       <c r="AD6" t="n">
-        <v>46463674.47931626</v>
+        <v>68307140.23523788</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JELLYJELLYUSDT</t>
+          <t>ASTERUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jelly-My-Jelly</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_too_early</t>
+          <t>risk_reward_unattractive | btc_regime_caution | entry_late</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1502,81 +1502,77 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>69.89</v>
+        <v>72.58</v>
       </c>
       <c r="I7" t="n">
-        <v>69.89</v>
+        <v>72.58</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N7" t="b">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07254456795701304</v>
+        <v>0.6967090037484529</v>
       </c>
       <c r="P7" t="n">
-        <v>0.05553</v>
+        <v>0.7095</v>
       </c>
       <c r="Q7" t="n">
-        <v>-23.45395173777198</v>
+        <v>1.835916599717913</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>early</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0.04886657722349436</v>
+        <v>0.6160450443860263</v>
       </c>
       <c r="T7" t="n">
-        <v>32.63923323321644</v>
+        <v>11.57785516312208</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07979902475271436</v>
+        <v>0.7663799041232983</v>
       </c>
       <c r="V7" t="n">
-        <v>0.08705348154841565</v>
+        <v>0.8360508044981435</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3063797463790655</v>
+        <v>0.8637178353942557</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6127594927581297</v>
+        <v>1.72743567078851</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.08588913144615723</v>
+        <v>0.09862627685803774</v>
       </c>
       <c r="Z7" t="n">
-        <v>2513.76236903</v>
+        <v>335672.329652</v>
       </c>
       <c r="AA7" t="n">
-        <v>3438.00253641</v>
+        <v>295272.436887</v>
       </c>
       <c r="AB7" t="n">
-        <v>94.291988</v>
+        <v>6.281063</v>
       </c>
       <c r="AC7" t="n">
-        <v>1248.971317</v>
+        <v>6.325461</v>
       </c>
       <c r="AD7" t="n">
-        <v>55697354.6766426</v>
+        <v>1758033101.175116</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1591,12 +1587,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETHFIUSDT</t>
+          <t>HUMAUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ether.fi</t>
+          <t>Huma Finance</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1606,7 +1602,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1620,15 +1616,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>69.72</v>
+        <v>70.58</v>
       </c>
       <c r="I8" t="n">
-        <v>69.72</v>
+        <v>70.58</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>none</t>
@@ -1643,13 +1643,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5128955151615413</v>
+        <v>0.01480590889108883</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5909</v>
+        <v>0.01665</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.20865020897881</v>
+        <v>12.45510236808944</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1657,40 +1657,40 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.4351343353948764</v>
+        <v>0.009558651609544486</v>
       </c>
       <c r="T8" t="n">
-        <v>15.1612126579374</v>
+        <v>35.44029157644276</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5641850666776955</v>
+        <v>0.01628649978019771</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6154746181938495</v>
+        <v>0.0177670906693066</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6595778468132416</v>
+        <v>0.2821647214281676</v>
       </c>
       <c r="X8" t="n">
-        <v>1.319155693626481</v>
+        <v>0.5643294428563346</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1014198782961349</v>
+        <v>0.06007810153200999</v>
       </c>
       <c r="Z8" t="n">
-        <v>167156.726897</v>
+        <v>8468.153620700001</v>
       </c>
       <c r="AA8" t="n">
-        <v>134848.106851</v>
+        <v>4719.6023864</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.00342</v>
+        <v>23.293643</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.51467</v>
+        <v>175.533387</v>
       </c>
       <c r="AD8" t="n">
-        <v>438078036.8556407</v>
+        <v>48735877.49914992</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1705,12 +1705,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HSKUSDT</t>
+          <t>AVAXUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HashKey Platform Token</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
+          <t>risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1734,36 +1734,40 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>68.33</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>68.33</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N9" t="b">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1647712192355553</v>
+        <v>9.167771118588441</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1742</v>
+        <v>9.859</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.722346905114173</v>
+        <v>7.539770272078816</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1771,51 +1775,47 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0.1430857449882901</v>
+        <v>8.035562824226808</v>
       </c>
       <c r="T9" t="n">
-        <v>13.16095999524277</v>
+        <v>12.34987522829822</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1812483411591109</v>
+        <v>10.08454823044729</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1977254630826664</v>
+        <v>11.00132534230613</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7598229919105191</v>
+        <v>0.8097247798169043</v>
       </c>
       <c r="X9" t="n">
-        <v>1.519645983821037</v>
+        <v>1.619449559633805</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1148105625717599</v>
+        <v>0.02028809089065397</v>
       </c>
       <c r="Z9" t="n">
-        <v>7354.298086999999</v>
+        <v>604673.1457999999</v>
       </c>
       <c r="AA9" t="n">
-        <v>7456.095217</v>
+        <v>647230.73742</v>
       </c>
       <c r="AB9" t="n">
-        <v>83.2081</v>
+        <v>3.975466</v>
       </c>
       <c r="AC9" t="n">
-        <v>140.581816</v>
+        <v>5.185459</v>
       </c>
       <c r="AD9" t="n">
-        <v>60315172.13616227</v>
+        <v>4259896452.993743</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>low_liquidity</t>
-        </is>
-      </c>
+      <c r="AF9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DEXEUSDT</t>
+          <t>JELLYJELLYUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DeXe</t>
+          <t>Jelly-My-Jelly</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1838,29 +1838,33 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_too_early</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>68</v>
+        <v>69.89</v>
       </c>
       <c r="I10" t="n">
-        <v>68</v>
+        <v>69.89</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>none</t>
@@ -1875,54 +1879,54 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.271727929672502</v>
+        <v>0.07254456795701304</v>
       </c>
       <c r="P10" t="n">
-        <v>5.007</v>
+        <v>0.056536</v>
       </c>
       <c r="Q10" t="n">
-        <v>17.21252107888503</v>
+        <v>-22.06721799831941</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>early</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>3.813657346888133</v>
+        <v>0.04886657722349436</v>
       </c>
       <c r="T10" t="n">
-        <v>10.72330893553624</v>
+        <v>32.63923323321644</v>
       </c>
       <c r="U10" t="n">
-        <v>4.698900722639753</v>
+        <v>0.07979902475271436</v>
       </c>
       <c r="V10" t="n">
-        <v>5.126073515607002</v>
+        <v>0.08705348154841565</v>
       </c>
       <c r="W10" t="n">
-        <v>0.9325479719101223</v>
+        <v>0.3063797463790655</v>
       </c>
       <c r="X10" t="n">
-        <v>1.865095943820243</v>
+        <v>0.6127594927581297</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.06009013520280648</v>
+        <v>0.2208539095559071</v>
       </c>
       <c r="Z10" t="n">
-        <v>5355.859799999999</v>
+        <v>5010.12955926</v>
       </c>
       <c r="AA10" t="n">
-        <v>1727.21575</v>
+        <v>8254.5697251</v>
       </c>
       <c r="AB10" t="n">
-        <v>166.788482</v>
+        <v>45.026513</v>
       </c>
       <c r="AC10" t="n">
-        <v>10141.64879</v>
+        <v>147.735194</v>
       </c>
       <c r="AD10" t="n">
-        <v>423550402.3537126</v>
+        <v>57098061.80026772</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1937,12 +1941,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KERNELUSDT</t>
+          <t>HSKUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KernelDAO</t>
+          <t>HashKey Platform Token</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1957,19 +1961,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>68</v>
+        <v>68.33</v>
       </c>
       <c r="I11" t="n">
-        <v>68</v>
+        <v>68.33</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -1989,13 +1993,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.08729454180475003</v>
+        <v>0.1647712192355553</v>
       </c>
       <c r="P11" t="n">
-        <v>0.09702</v>
+        <v>0.1771</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.14096940562757</v>
+        <v>7.482363013178639</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2003,47 +2007,51 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>0.07876377145832388</v>
+        <v>0.1430857449882901</v>
       </c>
       <c r="T11" t="n">
-        <v>9.77239833105117</v>
+        <v>13.16095999524277</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09602399598522504</v>
+        <v>0.1812483411591109</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1047534501657</v>
+        <v>0.1977254630826664</v>
       </c>
       <c r="W11" t="n">
-        <v>1.023290257031956</v>
+        <v>0.7598229919105191</v>
       </c>
       <c r="X11" t="n">
-        <v>2.046580514063909</v>
+        <v>1.519645983821037</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.09275003864584208</v>
+        <v>0.2259887005649626</v>
       </c>
       <c r="Z11" t="n">
-        <v>7200.732469</v>
+        <v>20835.538261</v>
       </c>
       <c r="AA11" t="n">
-        <v>4860.5145074</v>
+        <v>16142.342451</v>
       </c>
       <c r="AB11" t="n">
-        <v>59.907251</v>
+        <v>42.740003</v>
       </c>
       <c r="AC11" t="n">
-        <v>349.74818</v>
+        <v>80.919354</v>
       </c>
       <c r="AD11" t="n">
-        <v>27836537.21127053</v>
+        <v>61059743.28052828</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>low_liquidity</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2051,12 +2059,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RESOLVUSDT</t>
+          <t>ARIAUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Resolv</t>
+          <t>AriaAI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2103,13 +2111,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1043340400839963</v>
+        <v>0.09831510247616641</v>
       </c>
       <c r="P12" t="n">
-        <v>0.13192</v>
+        <v>0.135</v>
       </c>
       <c r="Q12" t="n">
-        <v>26.44003806791628</v>
+        <v>37.31359333397102</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2117,40 +2125,40 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0.08515131429352707</v>
+        <v>0.08119402198342962</v>
       </c>
       <c r="T12" t="n">
-        <v>18.3858746148676</v>
+        <v>17.41449692013218</v>
       </c>
       <c r="U12" t="n">
-        <v>0.114767444092396</v>
+        <v>0.1081466127237831</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1252008481007956</v>
+        <v>0.1179781229713997</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5438958009598079</v>
+        <v>0.5742342168058513</v>
       </c>
       <c r="X12" t="n">
-        <v>1.087791601919614</v>
+        <v>1.148468433611701</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.06080875646092789</v>
+        <v>0.221877080097622</v>
       </c>
       <c r="Z12" t="n">
-        <v>19562.4372455</v>
+        <v>2656.8859432</v>
       </c>
       <c r="AA12" t="n">
-        <v>19712.8213739</v>
+        <v>2753.0961213</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.95754</v>
+        <v>107.778439</v>
       </c>
       <c r="AC12" t="n">
-        <v>38.441606</v>
+        <v>3025.611539</v>
       </c>
       <c r="AD12" t="n">
-        <v>49060574.63594389</v>
+        <v>39872575.26747611</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2165,12 +2173,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BANANAS31USDT</t>
+          <t>ETHFIUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Banana For Scale</t>
+          <t>ether.fi</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2180,24 +2188,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>64.8</v>
+        <v>68</v>
       </c>
       <c r="I13" t="n">
-        <v>64.8</v>
+        <v>68</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
@@ -2217,13 +2225,13 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.006809922886232783</v>
+        <v>0.5128955151615413</v>
       </c>
       <c r="P13" t="n">
-        <v>0.007104</v>
+        <v>0.59</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.318361876927201</v>
+        <v>15.0331758729015</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2231,40 +2239,40 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0.005682970381366535</v>
+        <v>0.4351343353948764</v>
       </c>
       <c r="T13" t="n">
-        <v>16.54868232274027</v>
+        <v>15.1612126579374</v>
       </c>
       <c r="U13" t="n">
-        <v>0.007490915174856062</v>
+        <v>0.5641850666776955</v>
       </c>
       <c r="V13" t="n">
-        <v>0.008171907463479339</v>
+        <v>0.6154746181938495</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6042777186107787</v>
+        <v>0.6595778468132416</v>
       </c>
       <c r="X13" t="n">
-        <v>1.208555437221556</v>
+        <v>1.319155693626481</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.03236314260184683</v>
+        <v>0.05097272958966391</v>
       </c>
       <c r="Z13" t="n">
-        <v>11261.921104275</v>
+        <v>202525.275835</v>
       </c>
       <c r="AA13" t="n">
-        <v>16788.513957556</v>
+        <v>165672.928946</v>
       </c>
       <c r="AB13" t="n">
-        <v>12.625253</v>
+        <v>14.327143</v>
       </c>
       <c r="AC13" t="n">
-        <v>67.31598</v>
+        <v>24.183679</v>
       </c>
       <c r="AD13" t="n">
-        <v>70954642.91152386</v>
+        <v>439513508.1526854</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2279,12 +2287,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ASTERUSDT</t>
+          <t>SIGNUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Sign</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2294,7 +2302,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_not_confirmed | rebound_not_confirmed | entry_late</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_late</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2308,40 +2316,36 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>64.41</v>
+        <v>68</v>
       </c>
       <c r="I14" t="n">
-        <v>64.41</v>
+        <v>68</v>
       </c>
       <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>rebound_not_confirmed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N14" t="b">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6988536108816352</v>
+        <v>0.05121973312024061</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7054</v>
+        <v>0.05206</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9367325311671948</v>
+        <v>1.640513974929991</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -2349,40 +2353,40 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>0.674769322150654</v>
+        <v>0.04176686629942179</v>
       </c>
       <c r="T14" t="n">
-        <v>3.44625660595755</v>
+        <v>18.455517522178</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7687389719697988</v>
+        <v>0.05634170643226467</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8386243330579622</v>
+        <v>0.06146367974428872</v>
       </c>
       <c r="W14" t="n">
-        <v>2.901699189408295</v>
+        <v>0.5418433803323593</v>
       </c>
       <c r="X14" t="n">
-        <v>5.803398378816586</v>
+        <v>1.083686760664716</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.08504606661940949</v>
+        <v>0.01917729408381065</v>
       </c>
       <c r="Z14" t="n">
-        <v>304227.556439</v>
+        <v>5491.1523541</v>
       </c>
       <c r="AA14" t="n">
-        <v>289935.137229</v>
+        <v>4123.9236446</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.481129</v>
+        <v>58.737912</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.212991000000001</v>
+        <v>749.962973</v>
       </c>
       <c r="AD14" t="n">
-        <v>1747329530.404762</v>
+        <v>85635408.30683494</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2397,12 +2401,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ZROUSDT</t>
+          <t>UNIUSDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LayerZero</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2412,7 +2416,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2426,36 +2430,40 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>63.84</v>
+        <v>67.02</v>
       </c>
       <c r="I15" t="n">
-        <v>63.84</v>
+        <v>67.02</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N15" t="b">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.809059641689167</v>
+        <v>3.777165669911723</v>
       </c>
       <c r="P15" t="n">
-        <v>2.09</v>
+        <v>3.891</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.52963494606023</v>
+        <v>3.01374999235704</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -2463,40 +2471,40 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>1.45153993680352</v>
+        <v>3.203057950757883</v>
       </c>
       <c r="T15" t="n">
-        <v>19.76273731648897</v>
+        <v>15.19943177835928</v>
       </c>
       <c r="U15" t="n">
-        <v>1.989965605858084</v>
+        <v>4.154882236902896</v>
       </c>
       <c r="V15" t="n">
-        <v>2.170871570027</v>
+        <v>4.532598803894068</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5060027788588042</v>
+        <v>0.6579193318422513</v>
       </c>
       <c r="X15" t="n">
-        <v>1.012005557717607</v>
+        <v>1.3158386636845</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.04774409166867195</v>
+        <v>0.025697031992802</v>
       </c>
       <c r="Z15" t="n">
-        <v>250255.13371</v>
+        <v>147550.60096</v>
       </c>
       <c r="AA15" t="n">
-        <v>258891.88298</v>
+        <v>218684.19259</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.317355</v>
+        <v>5.191798</v>
       </c>
       <c r="AC15" t="n">
-        <v>18.04571</v>
+        <v>8.266341000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>634507928.4806006</v>
+        <v>2470263962.804405</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2511,12 +2519,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GRASSUSDT</t>
+          <t>JSTUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2526,24 +2534,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>63.7</v>
+        <v>66.97</v>
       </c>
       <c r="I16" t="n">
-        <v>63.7</v>
+        <v>66.97</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
@@ -2563,13 +2571,13 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3133178291831258</v>
+        <v>0.04695144039995708</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3503</v>
+        <v>0.05021</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.80340452163005</v>
+        <v>6.940276107154109</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -2577,40 +2585,40 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0.2799958140645221</v>
+        <v>0.04260101184770685</v>
       </c>
       <c r="T16" t="n">
-        <v>10.63521192058558</v>
+        <v>9.265804233461186</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3446496121014385</v>
+        <v>0.05164658443995279</v>
       </c>
       <c r="V16" t="n">
-        <v>0.375981395019751</v>
+        <v>0.05634172847994849</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9402727538173404</v>
+        <v>1.079237133446815</v>
       </c>
       <c r="X16" t="n">
-        <v>1.880545507634678</v>
+        <v>2.158474266893627</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.2284408909194811</v>
+        <v>0.07964954201513016</v>
       </c>
       <c r="Z16" t="n">
-        <v>15112.444803</v>
+        <v>3479.9788039</v>
       </c>
       <c r="AA16" t="n">
-        <v>11268.231585</v>
+        <v>6782.641749</v>
       </c>
       <c r="AB16" t="n">
-        <v>28.289455</v>
+        <v>17.769145</v>
       </c>
       <c r="AC16" t="n">
-        <v>88.34151</v>
+        <v>713.381829</v>
       </c>
       <c r="AD16" t="n">
-        <v>85506449.44058512</v>
+        <v>442428278.5201374</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2625,12 +2633,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>QUBICUSDT</t>
+          <t>SUIUSDT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qubic</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2640,50 +2648,54 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>61.6</v>
+        <v>66.88</v>
       </c>
       <c r="I17" t="n">
-        <v>61.6</v>
+        <v>66.88</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N17" t="b">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>6.141600255281821e-07</v>
+        <v>0.9381529251147179</v>
       </c>
       <c r="P17" t="n">
-        <v>6.975e-07</v>
+        <v>0.9794</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.56974908944046</v>
+        <v>4.396625942432397</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2691,40 +2703,40 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>5.413733749520684e-07</v>
+        <v>0.7847276119191102</v>
       </c>
       <c r="T17" t="n">
-        <v>11.85141454192117</v>
+        <v>16.35397695709863</v>
       </c>
       <c r="U17" t="n">
-        <v>6.755760280810004e-07</v>
+        <v>1.03196821762619</v>
       </c>
       <c r="V17" t="n">
-        <v>7.369920306338185e-07</v>
+        <v>1.125783510137661</v>
       </c>
       <c r="W17" t="n">
-        <v>0.843781133857711</v>
+        <v>0.611472061274942</v>
       </c>
       <c r="X17" t="n">
-        <v>1.687562267715421</v>
+        <v>1.222944122549883</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.2009184845005739</v>
+        <v>0.01021085413795885</v>
       </c>
       <c r="Z17" t="n">
-        <v>7116.111486257299</v>
+        <v>278567.215929</v>
       </c>
       <c r="AA17" t="n">
-        <v>1396.2923070611</v>
+        <v>236602.635881</v>
       </c>
       <c r="AB17" t="n">
-        <v>121.934412</v>
+        <v>2.37296</v>
       </c>
       <c r="AC17" t="n">
-        <v>467.635157</v>
+        <v>3.370794</v>
       </c>
       <c r="AD17" t="n">
-        <v>94820394.1330146</v>
+        <v>3821795788.528493</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2739,12 +2751,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SIGNUSDT</t>
+          <t>PIXELUSDT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sign</t>
+          <t>Pixels</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2754,29 +2766,33 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>60</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>none</t>
@@ -2791,13 +2807,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.05046366290388034</v>
+        <v>0.00523567538736384</v>
       </c>
       <c r="P18" t="n">
-        <v>0.05411</v>
+        <v>0.008170999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.22566870158623</v>
+        <v>56.0639152633581</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -2805,40 +2821,40 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>0.04109761567127466</v>
+        <v>0.004353499940786924</v>
       </c>
       <c r="T18" t="n">
-        <v>18.55998295336877</v>
+        <v>16.84931515628379</v>
       </c>
       <c r="U18" t="n">
-        <v>0.05551002919426837</v>
+        <v>0.005759242926100225</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0605563954846564</v>
+        <v>0.006282810464836608</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5387935983090399</v>
+        <v>0.593495931867035</v>
       </c>
       <c r="X18" t="n">
-        <v>1.077587196618079</v>
+        <v>1.186991863734069</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1661896408457203</v>
+        <v>0.1704199634814379</v>
       </c>
       <c r="Z18" t="n">
-        <v>3781.1641676</v>
+        <v>13604.7770279</v>
       </c>
       <c r="AA18" t="n">
-        <v>3557.2393987</v>
+        <v>3624.72400793</v>
       </c>
       <c r="AB18" t="n">
-        <v>64.661563</v>
+        <v>105.207247</v>
       </c>
       <c r="AC18" t="n">
-        <v>2749.865532</v>
+        <v>1039.71695</v>
       </c>
       <c r="AD18" t="n">
-        <v>87634425.46512368</v>
+        <v>26654763.02842948</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2853,12 +2869,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SPKUSDT</t>
+          <t>KERNELUSDT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spark</t>
+          <t>KernelDAO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2882,10 +2898,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>59.98</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>59.98</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -2905,13 +2921,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02037303259900328</v>
+        <v>0.07727730631024982</v>
       </c>
       <c r="P19" t="n">
-        <v>0.022</v>
+        <v>0.09218999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.985887192249996</v>
+        <v>19.29763652718341</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2919,40 +2935,40 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>0.01729128573308509</v>
+        <v>0.06021587471544896</v>
       </c>
       <c r="T19" t="n">
-        <v>15.12659860991415</v>
+        <v>22.07819139852431</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02241033585890361</v>
+        <v>0.0850050369412748</v>
       </c>
       <c r="V19" t="n">
-        <v>0.02444763911880394</v>
+        <v>0.09273276757229977</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6610871523652314</v>
+        <v>0.4529356512720692</v>
       </c>
       <c r="X19" t="n">
-        <v>1.32217430473046</v>
+        <v>0.9058713025441376</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.09099181073702996</v>
+        <v>0.1192347298249406</v>
       </c>
       <c r="Z19" t="n">
-        <v>533.9647105</v>
+        <v>6995.494066400001</v>
       </c>
       <c r="AA19" t="n">
-        <v>700.7587344999999</v>
+        <v>5263.0602222</v>
       </c>
       <c r="AB19" t="n">
-        <v>2276.155788</v>
+        <v>50.10114</v>
       </c>
       <c r="AC19" t="n">
-        <v>10542.607935</v>
+        <v>328.473586</v>
       </c>
       <c r="AD19" t="n">
-        <v>54222242.09075253</v>
+        <v>26442461.97062481</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2961,7 +2977,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>low_liquidity</t>
+          <t>overextended</t>
         </is>
       </c>
     </row>
@@ -2971,12 +2987,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HYPEUSDT</t>
+          <t>GRASSUSDT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>Grass</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3000,10 +3016,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>59.88</v>
+        <v>63.7</v>
       </c>
       <c r="I20" t="n">
-        <v>59.88</v>
+        <v>63.7</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
@@ -3023,13 +3039,13 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>32.09613629253965</v>
+        <v>0.3219236649775566</v>
       </c>
       <c r="P20" t="n">
-        <v>35</v>
+        <v>0.3493</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.047393371567015</v>
+        <v>8.503983397539884</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -3037,40 +3053,40 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>29.88866586910107</v>
+        <v>0.2871796839797419</v>
       </c>
       <c r="T20" t="n">
-        <v>6.877682732023061</v>
+        <v>10.79261476481917</v>
       </c>
       <c r="U20" t="n">
-        <v>35.30574992179362</v>
+        <v>0.3541160314753123</v>
       </c>
       <c r="V20" t="n">
-        <v>38.51536355104759</v>
+        <v>0.386308397973068</v>
       </c>
       <c r="W20" t="n">
-        <v>1.453978089660806</v>
+        <v>0.926559524073549</v>
       </c>
       <c r="X20" t="n">
-        <v>2.907956179321611</v>
+        <v>1.853119048147096</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.02855103497501216</v>
+        <v>0.2297530155083352</v>
       </c>
       <c r="Z20" t="n">
-        <v>49924.3747</v>
+        <v>14262.207429</v>
       </c>
       <c r="AA20" t="n">
-        <v>68965.6753</v>
+        <v>11273.142842</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.897409</v>
+        <v>40.055331</v>
       </c>
       <c r="AC20" t="n">
-        <v>11.855813</v>
+        <v>97.181894</v>
       </c>
       <c r="AD20" t="n">
-        <v>9003873488.356989</v>
+        <v>85075527.41483106</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3085,12 +3101,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OKBUSDT</t>
+          <t>PIUSDT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OKB</t>
+          <t>Pi</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3105,19 +3121,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>59.44</v>
+        <v>61.6</v>
       </c>
       <c r="I21" t="n">
-        <v>59.44</v>
+        <v>61.6</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
@@ -3137,13 +3153,13 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>85.88863072603141</v>
+        <v>0.2149298959986523</v>
       </c>
       <c r="P21" t="n">
-        <v>98.51900000000001</v>
+        <v>0.2259</v>
       </c>
       <c r="Q21" t="n">
-        <v>14.70551942346956</v>
+        <v>5.104038202957328</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -3151,40 +3167,40 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>70.62689155836354</v>
+        <v>0.1960463010276263</v>
       </c>
       <c r="T21" t="n">
-        <v>17.76921932350971</v>
+        <v>8.78593221444839</v>
       </c>
       <c r="U21" t="n">
-        <v>94.47749379863455</v>
+        <v>0.2364228855985176</v>
       </c>
       <c r="V21" t="n">
-        <v>103.0663568712377</v>
+        <v>0.2579158751983828</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5627709252690368</v>
+        <v>1.138183149598525</v>
       </c>
       <c r="X21" t="n">
-        <v>1.125541850538073</v>
+        <v>2.276366299197047</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.06191039231905881</v>
+        <v>0.03544528134691925</v>
       </c>
       <c r="Z21" t="n">
-        <v>33978.826989</v>
+        <v>10974.9120213</v>
       </c>
       <c r="AA21" t="n">
-        <v>32922.089988</v>
+        <v>9100.083884899999</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.20429</v>
+        <v>40.150566</v>
       </c>
       <c r="AC21" t="n">
-        <v>16.628542</v>
+        <v>113.794268</v>
       </c>
       <c r="AD21" t="n">
-        <v>2070312245.137269</v>
+        <v>2176747409.14006</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
